--- a/Assets/06 Data/ExcelData/Gun_Item_Table.xlsx
+++ b/Assets/06 Data/ExcelData/Gun_Item_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300D8229-0903-4888-BAE3-D4899B6DD098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526B5CF3-02EA-4791-9198-AA3DBFDBEFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="3795" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>가치</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -199,6 +199,14 @@
   </si>
   <si>
     <t>MaxStackSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소리 범위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>soundRange</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FC45F5-0ACC-4C1F-9F62-F8E7255584F7}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.75" style="1" bestFit="1" customWidth="1"/>
@@ -671,10 +679,10 @@
     <col min="11" max="11" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -720,8 +728,11 @@
       <c r="O1" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="P1" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -767,8 +778,11 @@
       <c r="O2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -814,8 +828,11 @@
       <c r="O3" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="P3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>258</v>
       </c>
@@ -861,8 +878,11 @@
       <c r="O4" s="1">
         <v>1</v>
       </c>
+      <c r="P4" s="1">
+        <v>24.6</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>780</v>
       </c>
@@ -908,8 +928,11 @@
       <c r="O5" s="1">
         <v>1</v>
       </c>
+      <c r="P5" s="1">
+        <v>41.7</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>254</v>
       </c>
@@ -954,6 +977,9 @@
       </c>
       <c r="O6" s="1">
         <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>20.3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/06 Data/ExcelData/Gun_Item_Table.xlsx
+++ b/Assets/06 Data/ExcelData/Gun_Item_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StudyUnity\Duckov\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526B5CF3-02EA-4791-9198-AA3DBFDBEFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DE9398-3FC1-4E82-A6D3-ADB11DE44F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3795" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="31920" yWindow="2490" windowWidth="18225" windowHeight="8595" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -206,7 +206,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>soundRange</t>
+    <t>SoundRange</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
